--- a/gear/management/commands/assets/pivots_skeleton.xlsx
+++ b/gear/management/commands/assets/pivots_skeleton.xlsx
@@ -8430,31 +8430,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" showAll="0" sortType="ascending">
-      <items count="21">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="13"/>
-        <item sd="0" x="14"/>
-        <item sd="0" x="15"/>
-        <item sd="0" x="16"/>
-        <item sd="0" x="17"/>
-        <item sd="0" x="18"/>
-        <item sd="0" x="19"/>
-        <item t="default" sd="0"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0" sortType="ascending">
       <items count="35">
         <item sd="0" x="0"/>
@@ -8654,10 +8630,9 @@
       </items>
     </pivotField>
   </pivotFields>
-  <rowFields count="6">
+  <rowFields count="5">
     <field x="6"/>
     <field x="7"/>
-    <field x="8"/>
     <field x="9"/>
     <field x="11"/>
     <field x="10"/>

--- a/gear/management/commands/assets/pivots_skeleton.xlsx
+++ b/gear/management/commands/assets/pivots_skeleton.xlsx
@@ -8,6 +8,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводная CF" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводная P&amp;L" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводная НДС" sheetId="5" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="raw_vat" sheetId="6" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="raw_cf" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="raw_pl" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
@@ -16,6 +18,7 @@
   <pivotCaches>
     <pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="538" r:id="rId5"/>
     <pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="531" r:id="rId6"/>
+    <pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="545" r:id="rId22"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -7433,6 +7436,490 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshOnLoad="1" missingItemsLimit="0" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0">
+  <cacheSource type="worksheet">
+    <worksheetSource name="raw_vat"/>
+  </cacheSource>
+  <cacheFields count="16">
+    <cacheField name="Дата" numFmtId="165">
+      <sharedItems count="1" containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-03-18T00:00:00" maxDate="2026-03-18T00:00:00">
+        <d v="2026-03-18T00:00:00"/>
+      </sharedItems>
+      <fieldGroup par="15" base="0">
+        <rangePr autoStart="1" autoEnd="1" groupBy="days" startDate="2023-09-22T00:00:00" endDate="2026-03-18T00:00:00" groupInterval="1"/>
+        <groupItems count="368">
+          <s v="&lt;2023-09-22"/>
+          <s v="01-Jan"/>
+          <s v="02-Jan"/>
+          <s v="03-Jan"/>
+          <s v="04-Jan"/>
+          <s v="05-Jan"/>
+          <s v="06-Jan"/>
+          <s v="07-Jan"/>
+          <s v="08-Jan"/>
+          <s v="09-Jan"/>
+          <s v="10-Jan"/>
+          <s v="11-Jan"/>
+          <s v="12-Jan"/>
+          <s v="13-Jan"/>
+          <s v="14-Jan"/>
+          <s v="15-Jan"/>
+          <s v="16-Jan"/>
+          <s v="17-Jan"/>
+          <s v="18-Jan"/>
+          <s v="19-Jan"/>
+          <s v="20-Jan"/>
+          <s v="21-Jan"/>
+          <s v="22-Jan"/>
+          <s v="23-Jan"/>
+          <s v="24-Jan"/>
+          <s v="25-Jan"/>
+          <s v="26-Jan"/>
+          <s v="27-Jan"/>
+          <s v="28-Jan"/>
+          <s v="29-Jan"/>
+          <s v="30-Jan"/>
+          <s v="31-Jan"/>
+          <s v="01-Feb"/>
+          <s v="02-Feb"/>
+          <s v="03-Feb"/>
+          <s v="04-Feb"/>
+          <s v="05-Feb"/>
+          <s v="06-Feb"/>
+          <s v="07-Feb"/>
+          <s v="08-Feb"/>
+          <s v="09-Feb"/>
+          <s v="10-Feb"/>
+          <s v="11-Feb"/>
+          <s v="12-Feb"/>
+          <s v="13-Feb"/>
+          <s v="14-Feb"/>
+          <s v="15-Feb"/>
+          <s v="16-Feb"/>
+          <s v="17-Feb"/>
+          <s v="18-Feb"/>
+          <s v="19-Feb"/>
+          <s v="20-Feb"/>
+          <s v="21-Feb"/>
+          <s v="22-Feb"/>
+          <s v="23-Feb"/>
+          <s v="24-Feb"/>
+          <s v="25-Feb"/>
+          <s v="26-Feb"/>
+          <s v="27-Feb"/>
+          <s v="28-Feb"/>
+          <s v="29-Feb"/>
+          <s v="01-Mar"/>
+          <s v="02-Mar"/>
+          <s v="03-Mar"/>
+          <s v="04-Mar"/>
+          <s v="05-Mar"/>
+          <s v="06-Mar"/>
+          <s v="07-Mar"/>
+          <s v="08-Mar"/>
+          <s v="09-Mar"/>
+          <s v="10-Mar"/>
+          <s v="11-Mar"/>
+          <s v="12-Mar"/>
+          <s v="13-Mar"/>
+          <s v="14-Mar"/>
+          <s v="15-Mar"/>
+          <s v="16-Mar"/>
+          <s v="17-Mar"/>
+          <s v="18-Mar"/>
+          <s v="19-Mar"/>
+          <s v="20-Mar"/>
+          <s v="21-Mar"/>
+          <s v="22-Mar"/>
+          <s v="23-Mar"/>
+          <s v="24-Mar"/>
+          <s v="25-Mar"/>
+          <s v="26-Mar"/>
+          <s v="27-Mar"/>
+          <s v="28-Mar"/>
+          <s v="29-Mar"/>
+          <s v="30-Mar"/>
+          <s v="31-Mar"/>
+          <s v="01-Apr"/>
+          <s v="02-Apr"/>
+          <s v="03-Apr"/>
+          <s v="04-Apr"/>
+          <s v="05-Apr"/>
+          <s v="06-Apr"/>
+          <s v="07-Apr"/>
+          <s v="08-Apr"/>
+          <s v="09-Apr"/>
+          <s v="10-Apr"/>
+          <s v="11-Apr"/>
+          <s v="12-Apr"/>
+          <s v="13-Apr"/>
+          <s v="14-Apr"/>
+          <s v="15-Apr"/>
+          <s v="16-Apr"/>
+          <s v="17-Apr"/>
+          <s v="18-Apr"/>
+          <s v="19-Apr"/>
+          <s v="20-Apr"/>
+          <s v="21-Apr"/>
+          <s v="22-Apr"/>
+          <s v="23-Apr"/>
+          <s v="24-Apr"/>
+          <s v="25-Apr"/>
+          <s v="26-Apr"/>
+          <s v="27-Apr"/>
+          <s v="28-Apr"/>
+          <s v="29-Apr"/>
+          <s v="30-Apr"/>
+          <s v="01-May"/>
+          <s v="02-May"/>
+          <s v="03-May"/>
+          <s v="04-May"/>
+          <s v="05-May"/>
+          <s v="06-May"/>
+          <s v="07-May"/>
+          <s v="08-May"/>
+          <s v="09-May"/>
+          <s v="10-May"/>
+          <s v="11-May"/>
+          <s v="12-May"/>
+          <s v="13-May"/>
+          <s v="14-May"/>
+          <s v="15-May"/>
+          <s v="16-May"/>
+          <s v="17-May"/>
+          <s v="18-May"/>
+          <s v="19-May"/>
+          <s v="20-May"/>
+          <s v="21-May"/>
+          <s v="22-May"/>
+          <s v="23-May"/>
+          <s v="24-May"/>
+          <s v="25-May"/>
+          <s v="26-May"/>
+          <s v="27-May"/>
+          <s v="28-May"/>
+          <s v="29-May"/>
+          <s v="30-May"/>
+          <s v="31-May"/>
+          <s v="01-Jun"/>
+          <s v="02-Jun"/>
+          <s v="03-Jun"/>
+          <s v="04-Jun"/>
+          <s v="05-Jun"/>
+          <s v="06-Jun"/>
+          <s v="07-Jun"/>
+          <s v="08-Jun"/>
+          <s v="09-Jun"/>
+          <s v="10-Jun"/>
+          <s v="11-Jun"/>
+          <s v="12-Jun"/>
+          <s v="13-Jun"/>
+          <s v="14-Jun"/>
+          <s v="15-Jun"/>
+          <s v="16-Jun"/>
+          <s v="17-Jun"/>
+          <s v="18-Jun"/>
+          <s v="19-Jun"/>
+          <s v="20-Jun"/>
+          <s v="21-Jun"/>
+          <s v="22-Jun"/>
+          <s v="23-Jun"/>
+          <s v="24-Jun"/>
+          <s v="25-Jun"/>
+          <s v="26-Jun"/>
+          <s v="27-Jun"/>
+          <s v="28-Jun"/>
+          <s v="29-Jun"/>
+          <s v="30-Jun"/>
+          <s v="01-Jul"/>
+          <s v="02-Jul"/>
+          <s v="03-Jul"/>
+          <s v="04-Jul"/>
+          <s v="05-Jul"/>
+          <s v="06-Jul"/>
+          <s v="07-Jul"/>
+          <s v="08-Jul"/>
+          <s v="09-Jul"/>
+          <s v="10-Jul"/>
+          <s v="11-Jul"/>
+          <s v="12-Jul"/>
+          <s v="13-Jul"/>
+          <s v="14-Jul"/>
+          <s v="15-Jul"/>
+          <s v="16-Jul"/>
+          <s v="17-Jul"/>
+          <s v="18-Jul"/>
+          <s v="19-Jul"/>
+          <s v="20-Jul"/>
+          <s v="21-Jul"/>
+          <s v="22-Jul"/>
+          <s v="23-Jul"/>
+          <s v="24-Jul"/>
+          <s v="25-Jul"/>
+          <s v="26-Jul"/>
+          <s v="27-Jul"/>
+          <s v="28-Jul"/>
+          <s v="29-Jul"/>
+          <s v="30-Jul"/>
+          <s v="31-Jul"/>
+          <s v="01-Aug"/>
+          <s v="02-Aug"/>
+          <s v="03-Aug"/>
+          <s v="04-Aug"/>
+          <s v="05-Aug"/>
+          <s v="06-Aug"/>
+          <s v="07-Aug"/>
+          <s v="08-Aug"/>
+          <s v="09-Aug"/>
+          <s v="10-Aug"/>
+          <s v="11-Aug"/>
+          <s v="12-Aug"/>
+          <s v="13-Aug"/>
+          <s v="14-Aug"/>
+          <s v="15-Aug"/>
+          <s v="16-Aug"/>
+          <s v="17-Aug"/>
+          <s v="18-Aug"/>
+          <s v="19-Aug"/>
+          <s v="20-Aug"/>
+          <s v="21-Aug"/>
+          <s v="22-Aug"/>
+          <s v="23-Aug"/>
+          <s v="24-Aug"/>
+          <s v="25-Aug"/>
+          <s v="26-Aug"/>
+          <s v="27-Aug"/>
+          <s v="28-Aug"/>
+          <s v="29-Aug"/>
+          <s v="30-Aug"/>
+          <s v="31-Aug"/>
+          <s v="01-Sep"/>
+          <s v="02-Sep"/>
+          <s v="03-Sep"/>
+          <s v="04-Sep"/>
+          <s v="05-Sep"/>
+          <s v="06-Sep"/>
+          <s v="07-Sep"/>
+          <s v="08-Sep"/>
+          <s v="09-Sep"/>
+          <s v="10-Sep"/>
+          <s v="11-Sep"/>
+          <s v="12-Sep"/>
+          <s v="13-Sep"/>
+          <s v="14-Sep"/>
+          <s v="15-Sep"/>
+          <s v="16-Sep"/>
+          <s v="17-Sep"/>
+          <s v="18-Sep"/>
+          <s v="19-Sep"/>
+          <s v="20-Sep"/>
+          <s v="21-Sep"/>
+          <s v="22-Sep"/>
+          <s v="23-Sep"/>
+          <s v="24-Sep"/>
+          <s v="25-Sep"/>
+          <s v="26-Sep"/>
+          <s v="27-Sep"/>
+          <s v="28-Sep"/>
+          <s v="29-Sep"/>
+          <s v="30-Sep"/>
+          <s v="01-Oct"/>
+          <s v="02-Oct"/>
+          <s v="03-Oct"/>
+          <s v="04-Oct"/>
+          <s v="05-Oct"/>
+          <s v="06-Oct"/>
+          <s v="07-Oct"/>
+          <s v="08-Oct"/>
+          <s v="09-Oct"/>
+          <s v="10-Oct"/>
+          <s v="11-Oct"/>
+          <s v="12-Oct"/>
+          <s v="13-Oct"/>
+          <s v="14-Oct"/>
+          <s v="15-Oct"/>
+          <s v="16-Oct"/>
+          <s v="17-Oct"/>
+          <s v="18-Oct"/>
+          <s v="19-Oct"/>
+          <s v="20-Oct"/>
+          <s v="21-Oct"/>
+          <s v="22-Oct"/>
+          <s v="23-Oct"/>
+          <s v="24-Oct"/>
+          <s v="25-Oct"/>
+          <s v="26-Oct"/>
+          <s v="27-Oct"/>
+          <s v="28-Oct"/>
+          <s v="29-Oct"/>
+          <s v="30-Oct"/>
+          <s v="31-Oct"/>
+          <s v="01-Nov"/>
+          <s v="02-Nov"/>
+          <s v="03-Nov"/>
+          <s v="04-Nov"/>
+          <s v="05-Nov"/>
+          <s v="06-Nov"/>
+          <s v="07-Nov"/>
+          <s v="08-Nov"/>
+          <s v="09-Nov"/>
+          <s v="10-Nov"/>
+          <s v="11-Nov"/>
+          <s v="12-Nov"/>
+          <s v="13-Nov"/>
+          <s v="14-Nov"/>
+          <s v="15-Nov"/>
+          <s v="16-Nov"/>
+          <s v="17-Nov"/>
+          <s v="18-Nov"/>
+          <s v="19-Nov"/>
+          <s v="20-Nov"/>
+          <s v="21-Nov"/>
+          <s v="22-Nov"/>
+          <s v="23-Nov"/>
+          <s v="24-Nov"/>
+          <s v="25-Nov"/>
+          <s v="26-Nov"/>
+          <s v="27-Nov"/>
+          <s v="28-Nov"/>
+          <s v="29-Nov"/>
+          <s v="30-Nov"/>
+          <s v="01-Dec"/>
+          <s v="02-Dec"/>
+          <s v="03-Dec"/>
+          <s v="04-Dec"/>
+          <s v="05-Dec"/>
+          <s v="06-Dec"/>
+          <s v="07-Dec"/>
+          <s v="08-Dec"/>
+          <s v="09-Dec"/>
+          <s v="10-Dec"/>
+          <s v="11-Dec"/>
+          <s v="12-Dec"/>
+          <s v="13-Dec"/>
+          <s v="14-Dec"/>
+          <s v="15-Dec"/>
+          <s v="16-Dec"/>
+          <s v="17-Dec"/>
+          <s v="18-Dec"/>
+          <s v="19-Dec"/>
+          <s v="20-Dec"/>
+          <s v="21-Dec"/>
+          <s v="22-Dec"/>
+          <s v="23-Dec"/>
+          <s v="24-Dec"/>
+          <s v="25-Dec"/>
+          <s v="26-Dec"/>
+          <s v="27-Dec"/>
+          <s v="28-Dec"/>
+          <s v="29-Dec"/>
+          <s v="30-Dec"/>
+          <s v="31-Dec"/>
+          <s v="&gt;2026-03-18"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Год" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Месяц" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Направление" numFmtId="0">
+      <sharedItems count="2">
+        <s v="1. Начисленный"/>
+        <s v="2. К вычету"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Строка" numFmtId="0">
+      <sharedItems count="1">
+        <s v="—"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Группа статей" numFmtId="0">
+      <sharedItems count="1">
+        <s v="—"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Статья" numFmtId="0">
+      <sharedItems count="1">
+        <s v="—"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Контрагент" numFmtId="0">
+      <sharedItems count="1">
+        <s v="—"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Договор" numFmtId="0">
+      <sharedItems count="1">
+        <s v="—"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="ID договора" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Источник" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="НДС, ₽" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="НДС к уплате, ₽" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Months" numFmtId="0" databaseField="0">
+      <fieldGroup base="0">
+        <rangePr autoStart="1" autoEnd="1" groupBy="months" startDate="2023-09-22T00:00:00" endDate="2026-03-18T00:00:00" groupInterval="1"/>
+        <groupItems count="14">
+          <s v="&lt;2023-09-22"/>
+          <s v="Jan"/>
+          <s v="Feb"/>
+          <s v="Mar"/>
+          <s v="Apr"/>
+          <s v="May"/>
+          <s v="Jun"/>
+          <s v="Jul"/>
+          <s v="Aug"/>
+          <s v="Sep"/>
+          <s v="Oct"/>
+          <s v="Nov"/>
+          <s v="Dec"/>
+          <s v="&gt;2026-03-18"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Quarters" numFmtId="0" databaseField="0">
+      <fieldGroup base="0">
+        <rangePr autoStart="1" autoEnd="1" groupBy="quarters" startDate="2023-09-22T00:00:00" endDate="2026-03-18T00:00:00" groupInterval="1"/>
+        <groupItems count="6">
+          <s v="&lt;2023-09-22"/>
+          <s v="Qtr1"/>
+          <s v="Qtr2"/>
+          <s v="Qtr3"/>
+          <s v="Qtr4"/>
+          <s v="&gt;2026-03-18"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Years" numFmtId="0" databaseField="0">
+      <fieldGroup base="0">
+        <rangePr autoStart="1" autoEnd="1" groupBy="years" startDate="2023-09-22T00:00:00" endDate="2026-03-18T00:00:00" groupInterval="1"/>
+        <groupItems count="6">
+          <s v="&lt;2023-09-22"/>
+          <s v="2023"/>
+          <s v="2024"/>
+          <s v="2025"/>
+          <s v="2026"/>
+          <s v="&gt;2026-03-18"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Pivot_raw_cf" cacheId="538" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" grandTotalCaption="ИТОГО">
   <location ref="A3:C7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
@@ -8668,6 +9155,497 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Pivot_raw_vat" cacheId="545" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" grandTotalCaption="ИТОГО">
+  <location ref="A3:C7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="16">
+    <pivotField axis="axisCol" numFmtId="165" showAll="0">
+      <items count="369">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item sd="0" x="62"/>
+        <item sd="0" x="63"/>
+        <item sd="0" x="64"/>
+        <item sd="0" x="65"/>
+        <item sd="0" x="66"/>
+        <item sd="0" x="67"/>
+        <item sd="0" x="68"/>
+        <item sd="0" x="69"/>
+        <item sd="0" x="70"/>
+        <item sd="0" x="71"/>
+        <item sd="0" x="72"/>
+        <item sd="0" x="73"/>
+        <item sd="0" x="74"/>
+        <item sd="0" x="75"/>
+        <item sd="0" x="76"/>
+        <item sd="0" x="77"/>
+        <item sd="0" x="78"/>
+        <item sd="0" x="79"/>
+        <item sd="0" x="80"/>
+        <item sd="0" x="81"/>
+        <item sd="0" x="82"/>
+        <item sd="0" x="83"/>
+        <item sd="0" x="84"/>
+        <item sd="0" x="85"/>
+        <item sd="0" x="86"/>
+        <item sd="0" x="87"/>
+        <item sd="0" x="88"/>
+        <item sd="0" x="89"/>
+        <item sd="0" x="90"/>
+        <item sd="0" x="91"/>
+        <item sd="0" x="92"/>
+        <item sd="0" x="93"/>
+        <item sd="0" x="94"/>
+        <item sd="0" x="95"/>
+        <item sd="0" x="96"/>
+        <item sd="0" x="97"/>
+        <item sd="0" x="98"/>
+        <item sd="0" x="99"/>
+        <item sd="0" x="100"/>
+        <item sd="0" x="101"/>
+        <item sd="0" x="102"/>
+        <item sd="0" x="103"/>
+        <item sd="0" x="104"/>
+        <item sd="0" x="105"/>
+        <item sd="0" x="106"/>
+        <item sd="0" x="107"/>
+        <item sd="0" x="108"/>
+        <item sd="0" x="109"/>
+        <item sd="0" x="110"/>
+        <item sd="0" x="111"/>
+        <item sd="0" x="112"/>
+        <item sd="0" x="113"/>
+        <item sd="0" x="114"/>
+        <item sd="0" x="115"/>
+        <item sd="0" x="116"/>
+        <item sd="0" x="117"/>
+        <item sd="0" x="118"/>
+        <item sd="0" x="119"/>
+        <item sd="0" x="120"/>
+        <item sd="0" x="121"/>
+        <item sd="0" x="122"/>
+        <item sd="0" x="123"/>
+        <item sd="0" x="124"/>
+        <item sd="0" x="125"/>
+        <item sd="0" x="126"/>
+        <item sd="0" x="127"/>
+        <item sd="0" x="128"/>
+        <item sd="0" x="129"/>
+        <item sd="0" x="130"/>
+        <item sd="0" x="131"/>
+        <item sd="0" x="132"/>
+        <item sd="0" x="133"/>
+        <item sd="0" x="134"/>
+        <item sd="0" x="135"/>
+        <item sd="0" x="136"/>
+        <item sd="0" x="137"/>
+        <item sd="0" x="138"/>
+        <item sd="0" x="139"/>
+        <item sd="0" x="140"/>
+        <item sd="0" x="141"/>
+        <item sd="0" x="142"/>
+        <item sd="0" x="143"/>
+        <item sd="0" x="144"/>
+        <item sd="0" x="145"/>
+        <item sd="0" x="146"/>
+        <item sd="0" x="147"/>
+        <item sd="0" x="148"/>
+        <item sd="0" x="149"/>
+        <item sd="0" x="150"/>
+        <item sd="0" x="151"/>
+        <item sd="0" x="152"/>
+        <item sd="0" x="153"/>
+        <item sd="0" x="154"/>
+        <item sd="0" x="155"/>
+        <item sd="0" x="156"/>
+        <item sd="0" x="157"/>
+        <item sd="0" x="158"/>
+        <item sd="0" x="159"/>
+        <item sd="0" x="160"/>
+        <item sd="0" x="161"/>
+        <item sd="0" x="162"/>
+        <item sd="0" x="163"/>
+        <item sd="0" x="164"/>
+        <item sd="0" x="165"/>
+        <item sd="0" x="166"/>
+        <item sd="0" x="167"/>
+        <item sd="0" x="168"/>
+        <item sd="0" x="169"/>
+        <item sd="0" x="170"/>
+        <item sd="0" x="171"/>
+        <item sd="0" x="172"/>
+        <item sd="0" x="173"/>
+        <item sd="0" x="174"/>
+        <item sd="0" x="175"/>
+        <item sd="0" x="176"/>
+        <item sd="0" x="177"/>
+        <item sd="0" x="178"/>
+        <item sd="0" x="179"/>
+        <item sd="0" x="180"/>
+        <item sd="0" x="181"/>
+        <item sd="0" x="182"/>
+        <item sd="0" x="183"/>
+        <item sd="0" x="184"/>
+        <item sd="0" x="185"/>
+        <item sd="0" x="186"/>
+        <item sd="0" x="187"/>
+        <item sd="0" x="188"/>
+        <item sd="0" x="189"/>
+        <item sd="0" x="190"/>
+        <item sd="0" x="191"/>
+        <item sd="0" x="192"/>
+        <item sd="0" x="193"/>
+        <item sd="0" x="194"/>
+        <item sd="0" x="195"/>
+        <item sd="0" x="196"/>
+        <item sd="0" x="197"/>
+        <item sd="0" x="198"/>
+        <item sd="0" x="199"/>
+        <item sd="0" x="200"/>
+        <item sd="0" x="201"/>
+        <item sd="0" x="202"/>
+        <item sd="0" x="203"/>
+        <item sd="0" x="204"/>
+        <item sd="0" x="205"/>
+        <item sd="0" x="206"/>
+        <item sd="0" x="207"/>
+        <item sd="0" x="208"/>
+        <item sd="0" x="209"/>
+        <item sd="0" x="210"/>
+        <item sd="0" x="211"/>
+        <item sd="0" x="212"/>
+        <item sd="0" x="213"/>
+        <item sd="0" x="214"/>
+        <item sd="0" x="215"/>
+        <item sd="0" x="216"/>
+        <item sd="0" x="217"/>
+        <item sd="0" x="218"/>
+        <item sd="0" x="219"/>
+        <item sd="0" x="220"/>
+        <item sd="0" x="221"/>
+        <item sd="0" x="222"/>
+        <item sd="0" x="223"/>
+        <item sd="0" x="224"/>
+        <item sd="0" x="225"/>
+        <item sd="0" x="226"/>
+        <item sd="0" x="227"/>
+        <item sd="0" x="228"/>
+        <item sd="0" x="229"/>
+        <item sd="0" x="230"/>
+        <item sd="0" x="231"/>
+        <item sd="0" x="232"/>
+        <item sd="0" x="233"/>
+        <item sd="0" x="234"/>
+        <item sd="0" x="235"/>
+        <item sd="0" x="236"/>
+        <item sd="0" x="237"/>
+        <item sd="0" x="238"/>
+        <item sd="0" x="239"/>
+        <item sd="0" x="240"/>
+        <item sd="0" x="241"/>
+        <item sd="0" x="242"/>
+        <item sd="0" x="243"/>
+        <item sd="0" x="244"/>
+        <item sd="0" x="245"/>
+        <item sd="0" x="246"/>
+        <item sd="0" x="247"/>
+        <item sd="0" x="248"/>
+        <item sd="0" x="249"/>
+        <item sd="0" x="250"/>
+        <item sd="0" x="251"/>
+        <item sd="0" x="252"/>
+        <item sd="0" x="253"/>
+        <item sd="0" x="254"/>
+        <item sd="0" x="255"/>
+        <item sd="0" x="256"/>
+        <item sd="0" x="257"/>
+        <item sd="0" x="258"/>
+        <item sd="0" x="259"/>
+        <item sd="0" x="260"/>
+        <item sd="0" x="261"/>
+        <item sd="0" x="262"/>
+        <item sd="0" x="263"/>
+        <item sd="0" x="264"/>
+        <item sd="0" x="265"/>
+        <item sd="0" x="266"/>
+        <item sd="0" x="267"/>
+        <item sd="0" x="268"/>
+        <item sd="0" x="269"/>
+        <item sd="0" x="270"/>
+        <item sd="0" x="271"/>
+        <item sd="0" x="272"/>
+        <item sd="0" x="273"/>
+        <item sd="0" x="274"/>
+        <item sd="0" x="275"/>
+        <item sd="0" x="276"/>
+        <item sd="0" x="277"/>
+        <item sd="0" x="278"/>
+        <item sd="0" x="279"/>
+        <item sd="0" x="280"/>
+        <item sd="0" x="281"/>
+        <item sd="0" x="282"/>
+        <item sd="0" x="283"/>
+        <item sd="0" x="284"/>
+        <item sd="0" x="285"/>
+        <item sd="0" x="286"/>
+        <item sd="0" x="287"/>
+        <item sd="0" x="288"/>
+        <item sd="0" x="289"/>
+        <item sd="0" x="290"/>
+        <item sd="0" x="291"/>
+        <item sd="0" x="292"/>
+        <item sd="0" x="293"/>
+        <item sd="0" x="294"/>
+        <item sd="0" x="295"/>
+        <item sd="0" x="296"/>
+        <item sd="0" x="297"/>
+        <item sd="0" x="298"/>
+        <item sd="0" x="299"/>
+        <item sd="0" x="300"/>
+        <item sd="0" x="301"/>
+        <item sd="0" x="302"/>
+        <item sd="0" x="303"/>
+        <item sd="0" x="304"/>
+        <item sd="0" x="305"/>
+        <item sd="0" x="306"/>
+        <item sd="0" x="307"/>
+        <item sd="0" x="308"/>
+        <item sd="0" x="309"/>
+        <item sd="0" x="310"/>
+        <item sd="0" x="311"/>
+        <item sd="0" x="312"/>
+        <item sd="0" x="313"/>
+        <item sd="0" x="314"/>
+        <item sd="0" x="315"/>
+        <item sd="0" x="316"/>
+        <item sd="0" x="317"/>
+        <item sd="0" x="318"/>
+        <item sd="0" x="319"/>
+        <item sd="0" x="320"/>
+        <item sd="0" x="321"/>
+        <item sd="0" x="322"/>
+        <item sd="0" x="323"/>
+        <item sd="0" x="324"/>
+        <item sd="0" x="325"/>
+        <item sd="0" x="326"/>
+        <item sd="0" x="327"/>
+        <item sd="0" x="328"/>
+        <item sd="0" x="329"/>
+        <item sd="0" x="330"/>
+        <item sd="0" x="331"/>
+        <item sd="0" x="332"/>
+        <item sd="0" x="333"/>
+        <item sd="0" x="334"/>
+        <item sd="0" x="335"/>
+        <item sd="0" x="336"/>
+        <item sd="0" x="337"/>
+        <item sd="0" x="338"/>
+        <item sd="0" x="339"/>
+        <item sd="0" x="340"/>
+        <item sd="0" x="341"/>
+        <item sd="0" x="342"/>
+        <item sd="0" x="343"/>
+        <item sd="0" x="344"/>
+        <item sd="0" x="345"/>
+        <item sd="0" x="346"/>
+        <item sd="0" x="347"/>
+        <item sd="0" x="348"/>
+        <item sd="0" x="349"/>
+        <item sd="0" x="350"/>
+        <item sd="0" x="351"/>
+        <item sd="0" x="352"/>
+        <item sd="0" x="353"/>
+        <item sd="0" x="354"/>
+        <item sd="0" x="355"/>
+        <item sd="0" x="356"/>
+        <item sd="0" x="357"/>
+        <item sd="0" x="358"/>
+        <item sd="0" x="359"/>
+        <item sd="0" x="360"/>
+        <item sd="0" x="361"/>
+        <item sd="0" x="362"/>
+        <item sd="0" x="363"/>
+        <item sd="0" x="364"/>
+        <item sd="0" x="365"/>
+        <item sd="0" x="366"/>
+        <item sd="0" x="367"/>
+        <item t="default" sd="0"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="2">
+        <item sd="0" x="0"/>
+        <item t="default" sd="0"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="2">
+        <item sd="0" x="0"/>
+        <item t="default" sd="0"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="2">
+        <item sd="0" x="0"/>
+        <item t="default" sd="0"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="2">
+        <item sd="0" x="0"/>
+        <item t="default" sd="0"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default" sd="0"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="7">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item t="default" sd="0"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="6">
+    <field x="3"/>
+    <field x="4"/>
+    <field x="5"/>
+    <field x="6"/>
+    <field x="7"/>
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="3">
+    <field x="15"/>
+    <field x="13"/>
+    <field x="0"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="в российских рублях (RUB)" fld="12" baseField="0" baseItem="0" numFmtId="171"/>
+  </dataFields>
+  <pivotTableStyleInfo name="ManpackPivotGreen" showRowHeaders="1" showColHeaders="1" showRowStripes="1" showColStripes="0" showLastColumn="1"/>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="raw_cf" displayName="raw_cf" comment="Raw cash flow data" ref="A1:O2" headerRowCount="1" totalsRowShown="0" headerRowDxfId="1194" dataDxfId="1193">
   <autoFilter ref="A1:O2"/>
@@ -8712,6 +9690,28 @@
     <tableColumn id="14" name="cr"/>
     <tableColumn id="15" name="amount"/>
     <tableColumn id="16" name="description"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="raw_vat" displayName="raw_vat" ref="A1:M2" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A1:M2"/>
+  <tableColumns count="13">
+    <tableColumn id="1" name="Дата"/>
+    <tableColumn id="2" name="Год"/>
+    <tableColumn id="3" name="Месяц"/>
+    <tableColumn id="4" name="Направление"/>
+    <tableColumn id="5" name="Строка"/>
+    <tableColumn id="6" name="Группа статей"/>
+    <tableColumn id="7" name="Статья"/>
+    <tableColumn id="8" name="Контрагент"/>
+    <tableColumn id="9" name="Договор"/>
+    <tableColumn id="10" name="ID договора"/>
+    <tableColumn id="11" name="Источник"/>
+    <tableColumn id="12" name="НДС, ₽"/>
+    <tableColumn id="13" name="НДС к уплате, ₽"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -16212,4 +17212,374 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor theme="9" tint="0.7999816888943144"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <cols>
+    <col width="42.33203125" bestFit="1" customWidth="1" style="24" min="1" max="1"/>
+    <col width="13.6640625" bestFit="1" customWidth="1" style="24" min="2" max="2"/>
+    <col width="13.33203125" bestFit="1" customWidth="1" style="24" min="3" max="4"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" style="24" min="5" max="7"/>
+    <col width="8.5" bestFit="1" customWidth="1" style="24" min="8" max="16"/>
+    <col width="14.6640625" bestFit="1" customWidth="1" style="24" min="17" max="17"/>
+    <col width="15.5" bestFit="1" customWidth="1" style="24" min="18" max="43"/>
+    <col width="10.83203125" customWidth="1" style="24" min="44" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>СВОДНАЯ: НДС ПО ОПЕРАЦИЯМ (СПРАВОЧНО)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>в российских рублях (RUB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1"/>
+    <row r="31" ht="16" customHeight="1"/>
+    <row r="32" ht="16" customHeight="1"/>
+    <row r="33" ht="16" customHeight="1"/>
+    <row r="34" ht="16" customHeight="1"/>
+    <row r="35" ht="16" customHeight="1"/>
+    <row r="36" ht="16" customHeight="1"/>
+    <row r="37" ht="16" customHeight="1"/>
+    <row r="38" ht="16" customHeight="1"/>
+    <row r="39" ht="16" customHeight="1"/>
+    <row r="40" ht="16" customHeight="1"/>
+    <row r="41" ht="16" customHeight="1"/>
+    <row r="42" ht="16" customHeight="1"/>
+    <row r="43" ht="16" customHeight="1"/>
+    <row r="44" ht="16" customHeight="1"/>
+    <row r="45" ht="16" customHeight="1"/>
+    <row r="46" ht="16" customHeight="1"/>
+    <row r="47" ht="16" customHeight="1"/>
+    <row r="48" ht="16" customHeight="1"/>
+    <row r="49" ht="16" customHeight="1"/>
+    <row r="50" ht="16" customHeight="1"/>
+    <row r="51" ht="16" customHeight="1"/>
+    <row r="52" ht="16" customHeight="1"/>
+    <row r="53" ht="16" customHeight="1"/>
+    <row r="54" ht="16" customHeight="1"/>
+    <row r="55" ht="16" customHeight="1"/>
+    <row r="56" ht="16" customHeight="1"/>
+    <row r="57" ht="16" customHeight="1"/>
+    <row r="58" ht="16" customHeight="1"/>
+    <row r="59" ht="16" customHeight="1"/>
+    <row r="60" ht="16" customHeight="1"/>
+    <row r="61" ht="16" customHeight="1"/>
+    <row r="62" ht="16" customHeight="1"/>
+    <row r="63" ht="16" customHeight="1"/>
+    <row r="64" ht="16" customHeight="1"/>
+    <row r="65" ht="16" customHeight="1"/>
+    <row r="66" ht="16" customHeight="1"/>
+    <row r="67" ht="16" customHeight="1"/>
+    <row r="68" ht="16" customHeight="1"/>
+    <row r="69" ht="16" customHeight="1"/>
+    <row r="70" ht="16" customHeight="1"/>
+    <row r="71" ht="16" customHeight="1"/>
+    <row r="72" ht="16" customHeight="1"/>
+    <row r="73" ht="16" customHeight="1"/>
+    <row r="74" ht="16" customHeight="1"/>
+    <row r="75" ht="16" customHeight="1"/>
+    <row r="76" ht="16" customHeight="1"/>
+    <row r="77" ht="16" customHeight="1"/>
+    <row r="78" ht="16" customHeight="1"/>
+    <row r="79" ht="16" customHeight="1"/>
+    <row r="80" ht="16" customHeight="1"/>
+    <row r="81" ht="16" customHeight="1"/>
+    <row r="82" ht="16" customHeight="1"/>
+    <row r="83" ht="16" customHeight="1"/>
+    <row r="84" ht="16" customHeight="1"/>
+    <row r="85" ht="16" customHeight="1"/>
+    <row r="86" ht="16" customHeight="1"/>
+    <row r="87" ht="16" customHeight="1"/>
+    <row r="88" ht="16" customHeight="1"/>
+    <row r="89" ht="16" customHeight="1"/>
+    <row r="90" ht="16" customHeight="1"/>
+    <row r="91" ht="16" customHeight="1"/>
+    <row r="92" ht="16" customHeight="1"/>
+    <row r="93" ht="16" customHeight="1"/>
+    <row r="94" ht="16" customHeight="1"/>
+    <row r="95" ht="16" customHeight="1"/>
+    <row r="96" ht="16" customHeight="1"/>
+    <row r="97" ht="16" customHeight="1"/>
+    <row r="98" ht="16" customHeight="1"/>
+    <row r="99" ht="16" customHeight="1"/>
+    <row r="100" ht="16" customHeight="1"/>
+    <row r="101" ht="16" customHeight="1"/>
+    <row r="102" ht="16" customHeight="1"/>
+    <row r="103" ht="16" customHeight="1"/>
+    <row r="104" ht="16" customHeight="1"/>
+    <row r="105" ht="16" customHeight="1"/>
+    <row r="106" ht="16" customHeight="1"/>
+    <row r="107" ht="16" customHeight="1"/>
+    <row r="108" ht="16" customHeight="1"/>
+    <row r="109" ht="16" customHeight="1"/>
+    <row r="110" ht="16" customHeight="1"/>
+    <row r="111" ht="16" customHeight="1"/>
+    <row r="112" ht="16" customHeight="1"/>
+    <row r="113" ht="16" customHeight="1"/>
+    <row r="114" ht="16" customHeight="1"/>
+    <row r="115" ht="16" customHeight="1"/>
+    <row r="116" ht="16" customHeight="1"/>
+    <row r="117" ht="16" customHeight="1"/>
+    <row r="118" ht="16" customHeight="1"/>
+    <row r="119" ht="16" customHeight="1"/>
+    <row r="120" ht="16" customHeight="1"/>
+    <row r="121" ht="16" customHeight="1"/>
+    <row r="122" ht="16" customHeight="1"/>
+    <row r="123" ht="16" customHeight="1"/>
+    <row r="124" ht="16" customHeight="1"/>
+    <row r="125" ht="16" customHeight="1"/>
+    <row r="126" ht="16" customHeight="1"/>
+    <row r="127" ht="16" customHeight="1"/>
+    <row r="128" ht="16" customHeight="1"/>
+    <row r="129" ht="16" customHeight="1"/>
+    <row r="130" ht="16" customHeight="1"/>
+    <row r="131" ht="16" customHeight="1"/>
+    <row r="132" ht="16" customHeight="1"/>
+    <row r="133" ht="16" customHeight="1"/>
+    <row r="134" ht="16" customHeight="1"/>
+    <row r="135" ht="16" customHeight="1"/>
+    <row r="136" ht="16" customHeight="1"/>
+    <row r="137" ht="16" customHeight="1"/>
+    <row r="138" ht="16" customHeight="1"/>
+    <row r="139" ht="16" customHeight="1"/>
+    <row r="140" ht="16" customHeight="1"/>
+    <row r="141" ht="16" customHeight="1"/>
+    <row r="142" ht="16" customHeight="1"/>
+    <row r="143" ht="16" customHeight="1"/>
+    <row r="144" ht="16" customHeight="1"/>
+    <row r="145" ht="16" customHeight="1"/>
+    <row r="146" ht="16" customHeight="1"/>
+    <row r="147" ht="16" customHeight="1"/>
+    <row r="148" ht="16" customHeight="1"/>
+    <row r="149" ht="16" customHeight="1"/>
+    <row r="150" ht="16" customHeight="1"/>
+    <row r="151" ht="16" customHeight="1"/>
+    <row r="152" ht="16" customHeight="1"/>
+    <row r="153" ht="16" customHeight="1"/>
+    <row r="154" ht="16" customHeight="1"/>
+    <row r="155" ht="16" customHeight="1"/>
+    <row r="156" ht="16" customHeight="1"/>
+    <row r="157" ht="16" customHeight="1"/>
+    <row r="158" ht="16" customHeight="1"/>
+    <row r="159" ht="16" customHeight="1"/>
+    <row r="160" ht="16" customHeight="1"/>
+    <row r="161" ht="16" customHeight="1"/>
+    <row r="162" ht="16" customHeight="1"/>
+    <row r="163" ht="16" customHeight="1"/>
+    <row r="164" ht="16" customHeight="1"/>
+    <row r="165" ht="16" customHeight="1"/>
+    <row r="166" ht="16" customHeight="1"/>
+    <row r="167" ht="16" customHeight="1"/>
+    <row r="168" ht="16" customHeight="1"/>
+    <row r="169" ht="16" customHeight="1"/>
+    <row r="170" ht="16" customHeight="1"/>
+    <row r="171" ht="16" customHeight="1"/>
+    <row r="172" ht="16" customHeight="1"/>
+    <row r="173" ht="16" customHeight="1"/>
+    <row r="174" ht="16" customHeight="1"/>
+    <row r="175" ht="16" customHeight="1"/>
+    <row r="176" ht="16" customHeight="1"/>
+    <row r="177" ht="16" customHeight="1"/>
+    <row r="178" ht="16" customHeight="1"/>
+    <row r="179" ht="16" customHeight="1"/>
+    <row r="180" ht="16" customHeight="1"/>
+    <row r="181" ht="16" customHeight="1"/>
+    <row r="182" ht="16" customHeight="1"/>
+    <row r="183" ht="16" customHeight="1"/>
+    <row r="184" ht="16" customHeight="1"/>
+    <row r="185" ht="16" customHeight="1"/>
+    <row r="186" ht="16" customHeight="1"/>
+    <row r="187" ht="16" customHeight="1"/>
+    <row r="188" ht="16" customHeight="1"/>
+    <row r="189" ht="16" customHeight="1"/>
+    <row r="190" ht="16" customHeight="1"/>
+    <row r="191" ht="16" customHeight="1"/>
+    <row r="192" ht="16" customHeight="1"/>
+    <row r="193" ht="16" customHeight="1"/>
+    <row r="194" ht="16" customHeight="1"/>
+    <row r="195" ht="16" customHeight="1"/>
+    <row r="196" ht="16" customHeight="1"/>
+    <row r="197" ht="16" customHeight="1"/>
+    <row r="198" ht="16" customHeight="1"/>
+    <row r="199" ht="16" customHeight="1"/>
+    <row r="200" ht="16" customHeight="1"/>
+    <row r="201" ht="16" customHeight="1"/>
+    <row r="202" ht="16" customHeight="1"/>
+    <row r="203" ht="16" customHeight="1"/>
+    <row r="204" ht="16" customHeight="1"/>
+    <row r="205" ht="16" customHeight="1"/>
+    <row r="206" ht="16" customHeight="1"/>
+    <row r="207" ht="16" customHeight="1"/>
+    <row r="208" ht="16" customHeight="1"/>
+    <row r="209" ht="16" customHeight="1"/>
+    <row r="210" ht="16" customHeight="1"/>
+    <row r="211" ht="16" customHeight="1"/>
+    <row r="212" ht="16" customHeight="1"/>
+    <row r="213" ht="16" customHeight="1"/>
+    <row r="214" ht="16" customHeight="1"/>
+    <row r="215" ht="16" customHeight="1"/>
+    <row r="216" ht="16" customHeight="1"/>
+    <row r="217" ht="16" customHeight="1"/>
+    <row r="218" ht="16" customHeight="1"/>
+    <row r="219" ht="16" customHeight="1"/>
+    <row r="220" ht="16" customHeight="1"/>
+    <row r="221" ht="16" customHeight="1"/>
+    <row r="222" ht="16" customHeight="1"/>
+    <row r="223" ht="16" customHeight="1"/>
+    <row r="224" ht="16" customHeight="1"/>
+    <row r="225" ht="16" customHeight="1"/>
+    <row r="226" ht="16" customHeight="1"/>
+    <row r="227" ht="16" customHeight="1"/>
+    <row r="228" ht="16" customHeight="1"/>
+    <row r="229" ht="16" customHeight="1"/>
+    <row r="230" ht="16" customHeight="1"/>
+    <row r="231" ht="16" customHeight="1"/>
+    <row r="232" ht="16" customHeight="1"/>
+    <row r="233" ht="16" customHeight="1"/>
+    <row r="234" ht="16" customHeight="1"/>
+    <row r="235" ht="16" customHeight="1"/>
+    <row r="236" ht="16" customHeight="1"/>
+    <row r="237" ht="16" customHeight="1"/>
+    <row r="238" ht="16" customHeight="1"/>
+    <row r="239" ht="16" customHeight="1"/>
+    <row r="240" ht="16" customHeight="1"/>
+    <row r="241" ht="16" customHeight="1"/>
+    <row r="242" ht="16" customHeight="1"/>
+    <row r="243" ht="16" customHeight="1"/>
+    <row r="244" ht="16" customHeight="1"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor theme="3" tint="0.7999816888943144"/>
+  </sheetPr>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Год</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Месяц</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Направление</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Строка</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Группа статей</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>Контрагент</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>Договор</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>ID договора</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>НДС, ₽</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>НДС к уплате, ₽</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/gear/management/commands/assets/pivots_skeleton.xlsx
+++ b/gear/management/commands/assets/pivots_skeleton.xlsx
@@ -7866,7 +7866,7 @@
     <cacheField name="НДС, ₽" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="НДС к уплате, ₽" numFmtId="0">
+    <cacheField name="НДС: к уплате −, к вычету +, ₽" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="Months" numFmtId="0" databaseField="0">
@@ -9711,7 +9711,7 @@
     <tableColumn id="10" name="ID договора"/>
     <tableColumn id="11" name="Источник"/>
     <tableColumn id="12" name="НДС, ₽"/>
-    <tableColumn id="13" name="НДС к уплате, ₽"/>
+    <tableColumn id="13" name="НДС: к уплате −, к вычету +, ₽"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17572,7 +17572,7 @@
       </c>
       <c r="M1" s="9" t="inlineStr">
         <is>
-          <t>НДС к уплате, ₽</t>
+          <t>НДС: к уплате −, к вычету +, ₽</t>
         </is>
       </c>
     </row>

--- a/gear/management/commands/assets/pivots_skeleton.xlsx
+++ b/gear/management/commands/assets/pivots_skeleton.xlsx
@@ -7827,9 +7827,10 @@
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="Направление" numFmtId="0">
-      <sharedItems count="2">
+      <sharedItems count="3">
         <s v="1. Начисленный"/>
         <s v="2. К вычету"/>
+        <s v="3. Корректировки сальдо"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Строка" numFmtId="0">
@@ -9535,9 +9536,10 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0" sortType="ascending">
-      <items count="3">
+      <items count="4">
         <item x="0"/>
         <item x="1"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>

--- a/gear/management/commands/assets/pivots_skeleton.xlsx
+++ b/gear/management/commands/assets/pivots_skeleton.xlsx
@@ -7827,10 +7827,11 @@
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="Направление" numFmtId="0">
-      <sharedItems count="3">
+      <sharedItems count="4">
         <s v="1. Начисленный"/>
         <s v="2. К вычету"/>
         <s v="3. Корректировки сальдо"/>
+        <s v="4. Оплачено в бюджет"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Строка" numFmtId="0">
@@ -9536,10 +9537,11 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0" sortType="ascending">
-      <items count="4">
+      <items count="5">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
+        <item x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
